--- a/data/benchmark/takashi_smiles_predictions.xlsx
+++ b/data/benchmark/takashi_smiles_predictions.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3894772231578827</v>
+        <v>0.9953882694244385</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1365273743867874</v>
+        <v>0.9915816187858582</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.2283442765474319</v>
+        <v>0.9855098724365234</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.2228386998176575</v>
+        <v>0.9791429042816162</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.3882738351821899</v>
+        <v>0.9970616698265076</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3898162543773651</v>
+        <v>0.9988324046134949</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2228386998176575</v>
+        <v>0.9791429042816162</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1450939774513245</v>
+        <v>0.9901725053787231</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.2583592534065247</v>
+        <v>0.9890275001525879</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.3158439993858337</v>
+        <v>0.9904808402061462</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2216856479644775</v>
+        <v>0.9881445169448853</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.3002983927726746</v>
+        <v>0.9977559447288513</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.2301336526870728</v>
+        <v>0.9803445339202881</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.2395530194044113</v>
+        <v>0.9895027875900269</v>
       </c>
     </row>
     <row r="16">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.2525869905948639</v>
+        <v>0.9960091114044189</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.3001226782798767</v>
+        <v>0.9953570961952209</v>
       </c>
     </row>
     <row r="18">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.2455099672079086</v>
+        <v>0.9975468516349792</v>
       </c>
     </row>
     <row r="19">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1365273743867874</v>
+        <v>0.9915816187858582</v>
       </c>
     </row>
     <row r="20">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.2525869905948639</v>
+        <v>0.9960091114044189</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1168305352330208</v>
+        <v>0.9894862174987793</v>
       </c>
     </row>
     <row r="22">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.2470959722995758</v>
+        <v>0.9951624274253845</v>
       </c>
     </row>
     <row r="23">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.2276249080896378</v>
+        <v>0.9874383807182312</v>
       </c>
     </row>
     <row r="24">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.2126442492008209</v>
+        <v>0.9891637563705444</v>
       </c>
     </row>
     <row r="25">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1412395983934402</v>
+        <v>0.9846820831298828</v>
       </c>
     </row>
     <row r="26">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.2726033329963684</v>
+        <v>0.967674732208252</v>
       </c>
     </row>
     <row r="27">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.2972388565540314</v>
+        <v>0.9961865544319153</v>
       </c>
     </row>
     <row r="28">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.3017428517341614</v>
+        <v>0.9971428513526917</v>
       </c>
     </row>
     <row r="29">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.2477200329303741</v>
+        <v>0.9829298257827759</v>
       </c>
     </row>
     <row r="30">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.1705508828163147</v>
+        <v>0.9966366291046143</v>
       </c>
     </row>
     <row r="31">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.03594261407852173</v>
+        <v>0.9912619590759277</v>
       </c>
     </row>
     <row r="32">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.2228386998176575</v>
+        <v>0.9791429042816162</v>
       </c>
     </row>
     <row r="33">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.2455099672079086</v>
+        <v>0.9975468516349792</v>
       </c>
     </row>
     <row r="34">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.2519289255142212</v>
+        <v>0.9968595504760742</v>
       </c>
     </row>
     <row r="35">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.1993048340082169</v>
+        <v>0.9800295233726501</v>
       </c>
     </row>
     <row r="36">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.1257041692733765</v>
+        <v>0.9830542206764221</v>
       </c>
     </row>
     <row r="37">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.3070090711116791</v>
+        <v>0.99442058801651</v>
       </c>
     </row>
     <row r="38">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.2714993357658386</v>
+        <v>0.9814320802688599</v>
       </c>
     </row>
     <row r="39">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.2006015330553055</v>
+        <v>0.9852719306945801</v>
       </c>
     </row>
     <row r="40">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.3065883815288544</v>
+        <v>0.9984608888626099</v>
       </c>
     </row>
     <row r="41">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.3252266645431519</v>
+        <v>0.9944236874580383</v>
       </c>
     </row>
     <row r="42">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.2184863090515137</v>
+        <v>0.9801391363143921</v>
       </c>
     </row>
     <row r="43">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.2675903141498566</v>
+        <v>0.9920781254768372</v>
       </c>
     </row>
     <row r="44">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.1633979231119156</v>
+        <v>0.9974269270896912</v>
       </c>
     </row>
     <row r="45">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.2914808690547943</v>
+        <v>0.9987301230430603</v>
       </c>
     </row>
     <row r="46">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.346275269985199</v>
+        <v>0.9982226490974426</v>
       </c>
     </row>
     <row r="47">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.1759175509214401</v>
+        <v>0.9801921844482422</v>
       </c>
     </row>
     <row r="48">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.1830401569604874</v>
+        <v>0.9963175058364868</v>
       </c>
     </row>
     <row r="49">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.1630320399999619</v>
+        <v>0.9845847487449646</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.2533592283725739</v>
+        <v>0.9916650652885437</v>
       </c>
     </row>
     <row r="51">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.256368100643158</v>
+        <v>0.9918583035469055</v>
       </c>
     </row>
     <row r="52">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.1002566441893578</v>
+        <v>0.9857573509216309</v>
       </c>
     </row>
     <row r="53">
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.1365273743867874</v>
+        <v>0.9915816187858582</v>
       </c>
     </row>
     <row r="54">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.2264825105667114</v>
+        <v>0.9984055161476135</v>
       </c>
     </row>
     <row r="55">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.1362845450639725</v>
+        <v>0.9915416836738586</v>
       </c>
     </row>
     <row r="56">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.2653510272502899</v>
+        <v>0.9920198321342468</v>
       </c>
     </row>
     <row r="57">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.2671054899692535</v>
+        <v>0.990294337272644</v>
       </c>
     </row>
     <row r="58">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.2874853014945984</v>
+        <v>0.9947838187217712</v>
       </c>
     </row>
     <row r="59">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.2076718956232071</v>
+        <v>0.9944655299186707</v>
       </c>
     </row>
     <row r="60">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.2240435481071472</v>
+        <v>0.9879746437072754</v>
       </c>
     </row>
     <row r="61">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.03669207170605659</v>
+        <v>0.989996075630188</v>
       </c>
     </row>
     <row r="62">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.1465958505868912</v>
+        <v>0.9826976656913757</v>
       </c>
     </row>
     <row r="63">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.2260583639144897</v>
+        <v>0.9933644533157349</v>
       </c>
     </row>
     <row r="64">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.1592017114162445</v>
+        <v>0.9738784432411194</v>
       </c>
     </row>
     <row r="65">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.3013366758823395</v>
+        <v>0.99681156873703</v>
       </c>
     </row>
     <row r="66">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.2719723582267761</v>
+        <v>0.9956219792366028</v>
       </c>
     </row>
     <row r="67">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.2566999197006226</v>
+        <v>0.9879595041275024</v>
       </c>
     </row>
     <row r="68">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.1551768779754639</v>
+        <v>0.9990246295928955</v>
       </c>
     </row>
     <row r="69">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.2294227480888367</v>
+        <v>0.9940154552459717</v>
       </c>
     </row>
     <row r="70">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.002743051620200276</v>
+        <v>0.9834443330764771</v>
       </c>
     </row>
     <row r="71">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.3059210181236267</v>
+        <v>0.9957647323608398</v>
       </c>
     </row>
     <row r="72">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.2817544341087341</v>
+        <v>0.9848576784133911</v>
       </c>
     </row>
     <row r="73">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.1908298879861832</v>
+        <v>0.9930586814880371</v>
       </c>
     </row>
     <row r="74">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.2675050795078278</v>
+        <v>0.9932083487510681</v>
       </c>
     </row>
     <row r="75">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.232856884598732</v>
+        <v>0.984282910823822</v>
       </c>
     </row>
     <row r="76">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.1385603696107864</v>
+        <v>0.9674734473228455</v>
       </c>
     </row>
     <row r="77">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.1965923458337784</v>
+        <v>0.9731947779655457</v>
       </c>
     </row>
     <row r="78">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.3158439993858337</v>
+        <v>0.9904808402061462</v>
       </c>
     </row>
     <row r="79">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.1864310801029205</v>
+        <v>0.9755632877349854</v>
       </c>
     </row>
     <row r="80">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.06785538047552109</v>
+        <v>0.9442185163497925</v>
       </c>
     </row>
     <row r="81">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.2247758507728577</v>
+        <v>0.9870331287384033</v>
       </c>
     </row>
     <row r="82">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.2059892266988754</v>
+        <v>0.995179295539856</v>
       </c>
     </row>
     <row r="83">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.3669134974479675</v>
+        <v>0.9952789545059204</v>
       </c>
     </row>
     <row r="84">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.2422852963209152</v>
+        <v>0.9902811050415039</v>
       </c>
     </row>
     <row r="85">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.3311562538146973</v>
+        <v>0.9973509311676025</v>
       </c>
     </row>
     <row r="86">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.2168374806642532</v>
+        <v>0.9882352352142334</v>
       </c>
     </row>
     <row r="87">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.1284534782171249</v>
+        <v>0.9975341558456421</v>
       </c>
     </row>
     <row r="88">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.1170969232916832</v>
+        <v>0.9961469173431396</v>
       </c>
     </row>
     <row r="89">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.2510380148887634</v>
+        <v>0.9932015538215637</v>
       </c>
     </row>
     <row r="90">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.1478340178728104</v>
+        <v>0.9893805980682373</v>
       </c>
     </row>
     <row r="91">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.2483327835798264</v>
+        <v>0.9845681190490723</v>
       </c>
     </row>
     <row r="92">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.3723357915878296</v>
+        <v>0.9950575828552246</v>
       </c>
     </row>
     <row r="93">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.3026558756828308</v>
+        <v>0.9910954236984253</v>
       </c>
     </row>
     <row r="94">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.346275269985199</v>
+        <v>0.9982226490974426</v>
       </c>
     </row>
     <row r="95">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.3013366758823395</v>
+        <v>0.99681156873703</v>
       </c>
     </row>
     <row r="96">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.1624286025762558</v>
+        <v>0.9701704382896423</v>
       </c>
     </row>
     <row r="97">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.2152763307094574</v>
+        <v>0.9811574816703796</v>
       </c>
     </row>
     <row r="98">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.1530748605728149</v>
+        <v>0.996513307094574</v>
       </c>
     </row>
     <row r="99">
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.1584917604923248</v>
+        <v>0.9824557304382324</v>
       </c>
     </row>
     <row r="100">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.2266839891672134</v>
+        <v>0.9978227615356445</v>
       </c>
     </row>
     <row r="101">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.3032165169715881</v>
+        <v>0.9988167285919189</v>
       </c>
     </row>
     <row r="102">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.2001791447401047</v>
+        <v>0.9938774704933167</v>
       </c>
     </row>
     <row r="103">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.08577542752027512</v>
+        <v>0.9800864458084106</v>
       </c>
     </row>
     <row r="104">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.1927340924739838</v>
+        <v>0.9919123649597168</v>
       </c>
     </row>
     <row r="105">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.3569008111953735</v>
+        <v>0.9762671589851379</v>
       </c>
     </row>
     <row r="106">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.1914555132389069</v>
+        <v>0.9983036518096924</v>
       </c>
     </row>
     <row r="107">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.2226281464099884</v>
+        <v>0.9892069101333618</v>
       </c>
     </row>
     <row r="108">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.2872278690338135</v>
+        <v>0.9795051217079163</v>
       </c>
     </row>
     <row r="109">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.1806344538927078</v>
+        <v>0.9967909455299377</v>
       </c>
     </row>
     <row r="110">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.192198246717453</v>
+        <v>0.9931394457817078</v>
       </c>
     </row>
     <row r="111">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.3059210181236267</v>
+        <v>0.9957647323608398</v>
       </c>
     </row>
     <row r="112">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.256368100643158</v>
+        <v>0.9918583035469055</v>
       </c>
     </row>
     <row r="113">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.2675050795078278</v>
+        <v>0.9932083487510681</v>
       </c>
     </row>
     <row r="114">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.1439235210418701</v>
+        <v>0.9951215386390686</v>
       </c>
     </row>
     <row r="115">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.06043822318315506</v>
+        <v>0.9682457447052002</v>
       </c>
     </row>
     <row r="116">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.09726183116436005</v>
+        <v>0.9902514219284058</v>
       </c>
     </row>
     <row r="117">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.1697209924459457</v>
+        <v>0.9938129186630249</v>
       </c>
     </row>
     <row r="118">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.3816291093826294</v>
+        <v>0.9830407500267029</v>
       </c>
     </row>
     <row r="119">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.3962855041027069</v>
+        <v>0.9965201616287231</v>
       </c>
     </row>
     <row r="120">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.1324140429496765</v>
+        <v>0.997803270816803</v>
       </c>
     </row>
     <row r="121">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.1305958181619644</v>
+        <v>0.9856570959091187</v>
       </c>
     </row>
     <row r="122">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.2541259527206421</v>
+        <v>0.9981402158737183</v>
       </c>
     </row>
     <row r="123">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.192198246717453</v>
+        <v>0.9931394457817078</v>
       </c>
     </row>
     <row r="124">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.1934078931808472</v>
+        <v>0.9945101737976074</v>
       </c>
     </row>
     <row r="125">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.06529562920331955</v>
+        <v>0.995403528213501</v>
       </c>
     </row>
     <row r="126">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.3531942069530487</v>
+        <v>0.9923345446586609</v>
       </c>
     </row>
     <row r="127">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.07277087867259979</v>
+        <v>0.9592125415802002</v>
       </c>
     </row>
     <row r="128">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.2180909812450409</v>
+        <v>0.9991239905357361</v>
       </c>
     </row>
     <row r="129">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.2113464921712875</v>
+        <v>0.9974862337112427</v>
       </c>
     </row>
     <row r="130">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.280280590057373</v>
+        <v>0.978263795375824</v>
       </c>
     </row>
     <row r="131">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.09614413976669312</v>
+        <v>0.9622810482978821</v>
       </c>
     </row>
     <row r="132">
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.2598624229431152</v>
+        <v>0.9875730872154236</v>
       </c>
     </row>
     <row r="133">
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.1901985704898834</v>
+        <v>0.9920015335083008</v>
       </c>
     </row>
     <row r="134">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.1578285992145538</v>
+        <v>0.9980326294898987</v>
       </c>
     </row>
     <row r="135">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.2275944203138351</v>
+        <v>0.9885814785957336</v>
       </c>
     </row>
     <row r="136">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.1602703928947449</v>
+        <v>0.9853709936141968</v>
       </c>
     </row>
     <row r="137">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.1301006227731705</v>
+        <v>0.9990493655204773</v>
       </c>
     </row>
     <row r="138">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.2679100036621094</v>
+        <v>0.9976213574409485</v>
       </c>
     </row>
     <row r="139">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.2690794765949249</v>
+        <v>0.9916115403175354</v>
       </c>
     </row>
     <row r="140">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.008720151148736477</v>
+        <v>0.9843248128890991</v>
       </c>
     </row>
     <row r="141">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.1880626678466797</v>
+        <v>0.9921960830688477</v>
       </c>
     </row>
     <row r="142">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.220786839723587</v>
+        <v>0.9909693598747253</v>
       </c>
     </row>
     <row r="143">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.09774787724018097</v>
+        <v>0.9932984709739685</v>
       </c>
     </row>
     <row r="144">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.06687688827514648</v>
+        <v>0.9883955717086792</v>
       </c>
     </row>
     <row r="145">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.2045129388570786</v>
+        <v>0.9973461627960205</v>
       </c>
     </row>
     <row r="146">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.1964133828878403</v>
+        <v>0.9872894883155823</v>
       </c>
     </row>
     <row r="147">
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.2253048121929169</v>
+        <v>0.9927056431770325</v>
       </c>
     </row>
     <row r="148">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.1432788223028183</v>
+        <v>0.9978491067886353</v>
       </c>
     </row>
     <row r="149">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.1820361465215683</v>
+        <v>0.9476338028907776</v>
       </c>
     </row>
     <row r="150">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.2385365515947342</v>
+        <v>0.9833856225013733</v>
       </c>
     </row>
     <row r="151">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.1568615734577179</v>
+        <v>0.9897196292877197</v>
       </c>
     </row>
     <row r="152">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0.1372383087873459</v>
+        <v>0.9862579107284546</v>
       </c>
     </row>
     <row r="153">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.192198246717453</v>
+        <v>0.9931394457817078</v>
       </c>
     </row>
     <row r="154">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0.211028054356575</v>
+        <v>0.9887412190437317</v>
       </c>
     </row>
     <row r="155">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.05401027575135231</v>
+        <v>0.9922899603843689</v>
       </c>
     </row>
     <row r="156">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.2212087363004684</v>
+        <v>0.9891554713249207</v>
       </c>
     </row>
     <row r="157">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.09121237695217133</v>
+        <v>0.9576280117034912</v>
       </c>
     </row>
     <row r="158">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.1487767845392227</v>
+        <v>0.9886282086372375</v>
       </c>
     </row>
     <row r="159">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.08886000514030457</v>
+        <v>0.9976192116737366</v>
       </c>
     </row>
     <row r="160">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.2329267710447311</v>
+        <v>0.9966344237327576</v>
       </c>
     </row>
     <row r="161">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.0794130265712738</v>
+        <v>0.9880951642990112</v>
       </c>
     </row>
     <row r="162">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.2733547985553741</v>
+        <v>0.9915462136268616</v>
       </c>
     </row>
     <row r="163">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.3101725578308105</v>
+        <v>0.9977898597717285</v>
       </c>
     </row>
     <row r="164">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.2821338772773743</v>
+        <v>0.9918553829193115</v>
       </c>
     </row>
     <row r="165">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.1953367739915848</v>
+        <v>0.9692730903625488</v>
       </c>
     </row>
     <row r="166">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.0794130265712738</v>
+        <v>0.9880951642990112</v>
       </c>
     </row>
     <row r="167">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.1806014180183411</v>
+        <v>0.9979801774024963</v>
       </c>
     </row>
     <row r="168">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.3068307936191559</v>
+        <v>0.9865682125091553</v>
       </c>
     </row>
     <row r="169">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.0622142106294632</v>
+        <v>0.991664707660675</v>
       </c>
     </row>
     <row r="170">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.1762240678071976</v>
+        <v>0.9939242005348206</v>
       </c>
     </row>
     <row r="171">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.1188134253025055</v>
+        <v>0.9918970465660095</v>
       </c>
     </row>
     <row r="172">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.204118400812149</v>
+        <v>0.9932239055633545</v>
       </c>
     </row>
     <row r="173">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.2359255105257034</v>
+        <v>0.9989019632339478</v>
       </c>
     </row>
     <row r="174">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.06885524839162827</v>
+        <v>0.985216498374939</v>
       </c>
     </row>
     <row r="175">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.1060144081711769</v>
+        <v>0.9922952651977539</v>
       </c>
     </row>
     <row r="176">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.2167678028345108</v>
+        <v>0.9934321641921997</v>
       </c>
     </row>
     <row r="177">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.192198246717453</v>
+        <v>0.9931394457817078</v>
       </c>
     </row>
     <row r="178">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.1553206741809845</v>
+        <v>0.9855345487594604</v>
       </c>
     </row>
     <row r="179">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.1553206741809845</v>
+        <v>0.9855345487594604</v>
       </c>
     </row>
     <row r="180">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>0.3202095329761505</v>
+        <v>0.9979485869407654</v>
       </c>
     </row>
     <row r="181">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.1079692617058754</v>
+        <v>0.9946327209472656</v>
       </c>
     </row>
     <row r="182">
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.251838892698288</v>
+        <v>0.9782736897468567</v>
       </c>
     </row>
     <row r="183">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.04934969171881676</v>
+        <v>0.9908438920974731</v>
       </c>
     </row>
     <row r="184">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.1463405340909958</v>
+        <v>0.9860566854476929</v>
       </c>
     </row>
     <row r="185">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.2381599247455597</v>
+        <v>0.9988778233528137</v>
       </c>
     </row>
     <row r="186">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.2662623226642609</v>
+        <v>0.982664167881012</v>
       </c>
     </row>
     <row r="187">
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0.2241699397563934</v>
+        <v>0.9906745553016663</v>
       </c>
     </row>
     <row r="188">
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0.2359268069267273</v>
+        <v>0.9780929088592529</v>
       </c>
     </row>
     <row r="189">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.1534573584794998</v>
+        <v>0.9952882528305054</v>
       </c>
     </row>
     <row r="190">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.1913326233625412</v>
+        <v>0.939853847026825</v>
       </c>
     </row>
     <row r="191">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0.1830419152975082</v>
+        <v>0.9901581406593323</v>
       </c>
     </row>
     <row r="192">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.2121280431747437</v>
+        <v>0.943473756313324</v>
       </c>
     </row>
     <row r="193">
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0.1341798603534698</v>
+        <v>0.9340649247169495</v>
       </c>
     </row>
     <row r="194">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.2844721972942352</v>
+        <v>0.9649256467819214</v>
       </c>
     </row>
     <row r="195">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.2263137698173523</v>
+        <v>0.9894888997077942</v>
       </c>
     </row>
     <row r="196">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.08341823518276215</v>
+        <v>0.8680702447891235</v>
       </c>
     </row>
     <row r="197">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.2061941474676132</v>
+        <v>0.9713040590286255</v>
       </c>
     </row>
     <row r="198">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.07383488118648529</v>
+        <v>0.7798818349838257</v>
       </c>
     </row>
     <row r="199">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.04432984068989754</v>
+        <v>0.9736993908882141</v>
       </c>
     </row>
     <row r="200">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0.169743224978447</v>
+        <v>0.9878588318824768</v>
       </c>
     </row>
     <row r="201">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0.2398655265569687</v>
+        <v>0.9880749583244324</v>
       </c>
     </row>
     <row r="202">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.134046345949173</v>
+        <v>0.9750130772590637</v>
       </c>
     </row>
     <row r="203">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.04731781780719757</v>
+        <v>0.9892415404319763</v>
       </c>
     </row>
     <row r="204">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0.2666023969650269</v>
+        <v>0.9983494281768799</v>
       </c>
     </row>
     <row r="205">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.1758950501680374</v>
+        <v>0.9905129075050354</v>
       </c>
     </row>
     <row r="206">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.1806014180183411</v>
+        <v>0.9979801774024963</v>
       </c>
     </row>
     <row r="207">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0.2428591549396515</v>
+        <v>0.9966038465499878</v>
       </c>
     </row>
     <row r="208">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.181880384683609</v>
+        <v>0.9794113039970398</v>
       </c>
     </row>
     <row r="209">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.003707457100972533</v>
+        <v>0.9852110147476196</v>
       </c>
     </row>
     <row r="210">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.2629244327545166</v>
+        <v>0.9925872683525085</v>
       </c>
     </row>
     <row r="211">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.2579684257507324</v>
+        <v>0.991814911365509</v>
       </c>
     </row>
     <row r="212">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>0.0873618870973587</v>
+        <v>0.9814590215682983</v>
       </c>
     </row>
     <row r="213">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>0.1401929259300232</v>
+        <v>0.986034631729126</v>
       </c>
     </row>
     <row r="214">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>0.2932127118110657</v>
+        <v>0.9970173835754395</v>
       </c>
     </row>
     <row r="215">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.08160229027271271</v>
+        <v>0.9952101111412048</v>
       </c>
     </row>
     <row r="216">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>0.1703418791294098</v>
+        <v>0.9912541508674622</v>
       </c>
     </row>
     <row r="217">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0.3677914440631866</v>
+        <v>0.9979283809661865</v>
       </c>
     </row>
     <row r="218">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>0.1503941565752029</v>
+        <v>0.9900894165039062</v>
       </c>
     </row>
     <row r="219">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.2164067625999451</v>
+        <v>0.9610981941223145</v>
       </c>
     </row>
     <row r="220">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.2775565683841705</v>
+        <v>0.9956269264221191</v>
       </c>
     </row>
     <row r="221">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.27289879322052</v>
+        <v>0.9951441287994385</v>
       </c>
     </row>
     <row r="222">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.02632089890539646</v>
+        <v>0.9696486592292786</v>
       </c>
     </row>
     <row r="223">
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.3692061007022858</v>
+        <v>0.9737458229064941</v>
       </c>
     </row>
     <row r="224">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.2798424065113068</v>
+        <v>0.9697296023368835</v>
       </c>
     </row>
     <row r="225">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>0.3816242218017578</v>
+        <v>0.9892827272415161</v>
       </c>
     </row>
     <row r="226">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0.2615888714790344</v>
+        <v>0.9533518552780151</v>
       </c>
     </row>
     <row r="227">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.1012129783630371</v>
+        <v>0.996311366558075</v>
       </c>
     </row>
     <row r="228">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.125432088971138</v>
+        <v>0.995114803314209</v>
       </c>
     </row>
     <row r="229">
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.1709457784891129</v>
+        <v>0.9963051080703735</v>
       </c>
     </row>
     <row r="230">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.2296951711177826</v>
+        <v>0.9862653613090515</v>
       </c>
     </row>
     <row r="231">
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.1511886715888977</v>
+        <v>0.9877869486808777</v>
       </c>
     </row>
     <row r="232">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>0.1679977923631668</v>
+        <v>0.9934945702552795</v>
       </c>
     </row>
     <row r="233">
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.04287027195096016</v>
+        <v>0.9210926294326782</v>
       </c>
     </row>
     <row r="234">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.075631283223629</v>
+        <v>0.9837996959686279</v>
       </c>
     </row>
     <row r="235">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0.1993606984615326</v>
+        <v>0.995710015296936</v>
       </c>
     </row>
     <row r="236">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.02695173770189285</v>
+        <v>0.9884833693504333</v>
       </c>
     </row>
     <row r="237">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.1346227377653122</v>
+        <v>0.9988447427749634</v>
       </c>
     </row>
     <row r="238">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.01711434684693813</v>
+        <v>0.9775082468986511</v>
       </c>
     </row>
     <row r="239">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>0.1353615075349808</v>
+        <v>0.9790000319480896</v>
       </c>
     </row>
     <row r="240">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0.1387197822332382</v>
+        <v>0.9973764419555664</v>
       </c>
     </row>
     <row r="241">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>0.1086609736084938</v>
+        <v>0.9980890154838562</v>
       </c>
     </row>
     <row r="242">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.06251677870750427</v>
+        <v>0.8291151523590088</v>
       </c>
     </row>
     <row r="243">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.2530822455883026</v>
+        <v>0.9957749247550964</v>
       </c>
     </row>
     <row r="244">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.09380728751420975</v>
+        <v>0.9641790986061096</v>
       </c>
     </row>
     <row r="245">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.2115751951932907</v>
+        <v>0.9968413114547729</v>
       </c>
     </row>
     <row r="246">
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.1309954673051834</v>
+        <v>0.9961082339286804</v>
       </c>
     </row>
     <row r="247">
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0.1462472975254059</v>
+        <v>0.9920008182525635</v>
       </c>
     </row>
     <row r="248">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.1181052252650261</v>
+        <v>0.9990934133529663</v>
       </c>
     </row>
     <row r="249">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>0.2804678678512573</v>
+        <v>0.9829498529434204</v>
       </c>
     </row>
     <row r="250">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.175004243850708</v>
+        <v>0.9836875200271606</v>
       </c>
     </row>
     <row r="251">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.1856320202350616</v>
+        <v>0.9938581585884094</v>
       </c>
     </row>
     <row r="252">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.10260970890522</v>
+        <v>0.9944774508476257</v>
       </c>
     </row>
     <row r="253">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.1389700919389725</v>
+        <v>0.9949700236320496</v>
       </c>
     </row>
     <row r="254">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.1332656890153885</v>
+        <v>0.9871067404747009</v>
       </c>
     </row>
     <row r="255">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>0.2674391269683838</v>
+        <v>0.9964839220046997</v>
       </c>
     </row>
     <row r="256">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>0.1422510743141174</v>
+        <v>0.9751539826393127</v>
       </c>
     </row>
     <row r="257">
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.166701540350914</v>
+        <v>0.9461750388145447</v>
       </c>
     </row>
     <row r="258">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.1124706864356995</v>
+        <v>0.9899585843086243</v>
       </c>
     </row>
     <row r="259">
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0.2932127118110657</v>
+        <v>0.9970173835754395</v>
       </c>
     </row>
     <row r="260">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0.08240543305873871</v>
+        <v>0.9835789203643799</v>
       </c>
     </row>
     <row r="261">
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0.1931960135698318</v>
+        <v>0.9979945421218872</v>
       </c>
     </row>
     <row r="262">
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0.3617138862609863</v>
+        <v>0.9974309802055359</v>
       </c>
     </row>
     <row r="263">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.1051911190152168</v>
+        <v>0.9639275074005127</v>
       </c>
     </row>
     <row r="264">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.252662718296051</v>
+        <v>0.9982609152793884</v>
       </c>
     </row>
     <row r="265">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0.05594642087817192</v>
+        <v>0.9312425851821899</v>
       </c>
     </row>
     <row r="266">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.1478835195302963</v>
+        <v>0.9914520978927612</v>
       </c>
     </row>
     <row r="267">
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.1794226914644241</v>
+        <v>0.9900956153869629</v>
       </c>
     </row>
     <row r="268">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0.1768004149198532</v>
+        <v>0.9617002010345459</v>
       </c>
     </row>
     <row r="269">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0.08559810370206833</v>
+        <v>0.9686309099197388</v>
       </c>
     </row>
     <row r="270">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0.03398310020565987</v>
+        <v>0.993165910243988</v>
       </c>
     </row>
     <row r="271">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0.03897587582468987</v>
+        <v>0.9902862906455994</v>
       </c>
     </row>
     <row r="272">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0.2074229419231415</v>
+        <v>0.9972296357154846</v>
       </c>
     </row>
     <row r="273">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0.1580090224742889</v>
+        <v>0.9557744860649109</v>
       </c>
     </row>
     <row r="274">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.2650307714939117</v>
+        <v>0.9954805374145508</v>
       </c>
     </row>
     <row r="275">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.2734405100345612</v>
+        <v>0.9952738881111145</v>
       </c>
     </row>
     <row r="276">
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0.4065091013908386</v>
+        <v>0.9956633448600769</v>
       </c>
     </row>
     <row r="277">
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0.2034418284893036</v>
+        <v>0.9962472319602966</v>
       </c>
     </row>
     <row r="278">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.2993531227111816</v>
+        <v>0.9927840232849121</v>
       </c>
     </row>
     <row r="279">
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.06913104653358459</v>
+        <v>0.9875715970993042</v>
       </c>
     </row>
     <row r="280">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.06059874594211578</v>
+        <v>0.979616641998291</v>
       </c>
     </row>
     <row r="281">
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0.3675273060798645</v>
+        <v>0.9935240745544434</v>
       </c>
     </row>
     <row r="282">
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.104700893163681</v>
+        <v>0.997244119644165</v>
       </c>
     </row>
     <row r="283">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.1012628823518753</v>
+        <v>0.9738760590553284</v>
       </c>
     </row>
     <row r="284">
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.09378929436206818</v>
+        <v>0.9996681213378906</v>
       </c>
     </row>
     <row r="285">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>0.09188501536846161</v>
+        <v>0.9947420358657837</v>
       </c>
     </row>
     <row r="286">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.1049820110201836</v>
+        <v>0.9909092783927917</v>
       </c>
     </row>
     <row r="287">
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.1069688871502876</v>
+        <v>0.9601019024848938</v>
       </c>
     </row>
     <row r="288">
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.4056494235992432</v>
+        <v>0.9961003065109253</v>
       </c>
     </row>
     <row r="289">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>0.1750245541334152</v>
+        <v>0.9931150078773499</v>
       </c>
     </row>
     <row r="290">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.2224004715681076</v>
+        <v>0.9981402158737183</v>
       </c>
     </row>
     <row r="291">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>0.106758326292038</v>
+        <v>0.9907003045082092</v>
       </c>
     </row>
     <row r="292">
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>0.2037400007247925</v>
+        <v>0.9952917098999023</v>
       </c>
     </row>
     <row r="293">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>0.1051745191216469</v>
+        <v>0.9735367894172668</v>
       </c>
     </row>
     <row r="294">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>0.1281643211841583</v>
+        <v>0.9620380401611328</v>
       </c>
     </row>
     <row r="295">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>0.3272920548915863</v>
+        <v>0.9977033734321594</v>
       </c>
     </row>
     <row r="296">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>0.2203145027160645</v>
+        <v>0.9931784868240356</v>
       </c>
     </row>
     <row r="297">
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>0.1499260365962982</v>
+        <v>0.9936686158180237</v>
       </c>
     </row>
     <row r="298">
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>0.2880789935588837</v>
+        <v>0.9975066781044006</v>
       </c>
     </row>
     <row r="299">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>0.2489667534828186</v>
+        <v>0.992473840713501</v>
       </c>
     </row>
     <row r="300">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>0.08300931751728058</v>
+        <v>0.9930701851844788</v>
       </c>
     </row>
     <row r="301">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>0.0180730763822794</v>
+        <v>0.959119975566864</v>
       </c>
     </row>
     <row r="302">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>0.1354763507843018</v>
+        <v>0.9770508408546448</v>
       </c>
     </row>
     <row r="303">
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>0.05911857634782791</v>
+        <v>0.9940744042396545</v>
       </c>
     </row>
     <row r="304">
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>0.1502619683742523</v>
+        <v>0.9916816353797913</v>
       </c>
     </row>
     <row r="305">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>0.3798471391201019</v>
+        <v>0.9996793270111084</v>
       </c>
     </row>
     <row r="306">
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>0.3515203297138214</v>
+        <v>0.9958260059356689</v>
       </c>
     </row>
     <row r="307">
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>0.03029381297528744</v>
+        <v>0.9879222512245178</v>
       </c>
     </row>
     <row r="308">
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>0.123294435441494</v>
+        <v>0.9775277972221375</v>
       </c>
     </row>
     <row r="309">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>0.2375804334878922</v>
+        <v>0.9972161054611206</v>
       </c>
     </row>
     <row r="310">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>0.05189007893204689</v>
+        <v>0.9815125465393066</v>
       </c>
     </row>
     <row r="311">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>0.1004131436347961</v>
+        <v>0.9741033911705017</v>
       </c>
     </row>
     <row r="312">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>0.2139346301555634</v>
+        <v>0.9969488978385925</v>
       </c>
     </row>
     <row r="313">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>0.2664976418018341</v>
+        <v>0.9953508377075195</v>
       </c>
     </row>
     <row r="314">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>0.111479289829731</v>
+        <v>0.9845123291015625</v>
       </c>
     </row>
     <row r="315">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>0.072889544069767</v>
+        <v>0.9929458498954773</v>
       </c>
     </row>
     <row r="316">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>0.08183519542217255</v>
+        <v>0.994131863117218</v>
       </c>
     </row>
     <row r="317">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>0.002964043291285634</v>
+        <v>0.6506327390670776</v>
       </c>
     </row>
     <row r="318">
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>0.09207217395305634</v>
+        <v>0.9933027029037476</v>
       </c>
     </row>
     <row r="319">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>0.1527419686317444</v>
+        <v>0.9759119153022766</v>
       </c>
     </row>
     <row r="320">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>0.09267236292362213</v>
+        <v>0.9245592355728149</v>
       </c>
     </row>
     <row r="321">
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>0.3828268051147461</v>
+        <v>0.9956082701683044</v>
       </c>
     </row>
     <row r="322">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>0.1134526953101158</v>
+        <v>0.9973849654197693</v>
       </c>
     </row>
     <row r="323">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>0.2536743581295013</v>
+        <v>0.9980623126029968</v>
       </c>
     </row>
     <row r="324">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>0.2488295137882233</v>
+        <v>0.9988946318626404</v>
       </c>
     </row>
     <row r="325">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>0.05967402458190918</v>
+        <v>0.9945530891418457</v>
       </c>
     </row>
     <row r="326">
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>0.1994080692529678</v>
+        <v>0.9911661744117737</v>
       </c>
     </row>
     <row r="327">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>0.1087791174650192</v>
+        <v>0.8321387767791748</v>
       </c>
     </row>
     <row r="328">
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>0.03158938139677048</v>
+        <v>0.838883101940155</v>
       </c>
     </row>
     <row r="329">
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>0.3935456871986389</v>
+        <v>0.9986139535903931</v>
       </c>
     </row>
     <row r="330">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>0.2749478816986084</v>
+        <v>0.9980321526527405</v>
       </c>
     </row>
     <row r="331">
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>0.1611967831850052</v>
+        <v>0.9948199391365051</v>
       </c>
     </row>
     <row r="332">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>0.3327957093715668</v>
+        <v>0.9924502372741699</v>
       </c>
     </row>
     <row r="333">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>0.1794226914644241</v>
+        <v>0.9900956153869629</v>
       </c>
     </row>
     <row r="334">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>0.06955362856388092</v>
+        <v>0.9881792068481445</v>
       </c>
     </row>
     <row r="335">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>0.07547080516815186</v>
+        <v>0.9922903180122375</v>
       </c>
     </row>
     <row r="336">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>0.03433173149824142</v>
+        <v>0.913361132144928</v>
       </c>
     </row>
     <row r="337">
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>0.3139433860778809</v>
+        <v>0.9926450252532959</v>
       </c>
     </row>
     <row r="338">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>0.219700962305069</v>
+        <v>0.9986710548400879</v>
       </c>
     </row>
     <row r="339">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>0.06194678694009781</v>
+        <v>0.8114098310470581</v>
       </c>
     </row>
     <row r="340">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F340" t="n">
-        <v>0.1973191499710083</v>
+        <v>0.9822247624397278</v>
       </c>
     </row>
     <row r="341">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>0.1966025084257126</v>
+        <v>0.9969490170478821</v>
       </c>
     </row>
     <row r="342">
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>0.01706938073039055</v>
+        <v>0.9503487944602966</v>
       </c>
     </row>
     <row r="343">
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>0.1275404542684555</v>
+        <v>0.9939379692077637</v>
       </c>
     </row>
     <row r="344">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="F344" t="n">
-        <v>0.009390203282237053</v>
+        <v>0.9664238095283508</v>
       </c>
     </row>
     <row r="345">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>0.2929298877716064</v>
+        <v>0.9950968623161316</v>
       </c>
     </row>
     <row r="346">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="F346" t="n">
-        <v>0.3520203828811646</v>
+        <v>0.9964863061904907</v>
       </c>
     </row>
     <row r="347">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="F347" t="n">
-        <v>0.09106054902076721</v>
+        <v>0.9942183494567871</v>
       </c>
     </row>
     <row r="348">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="F348" t="n">
-        <v>0.3329795897006989</v>
+        <v>0.9962422847747803</v>
       </c>
     </row>
     <row r="349">
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>0.07847370207309723</v>
+        <v>0.9418619871139526</v>
       </c>
     </row>
     <row r="350">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>0.09714747220277786</v>
+        <v>0.977053701877594</v>
       </c>
     </row>
     <row r="351">
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="F351" t="n">
-        <v>0.06202602386474609</v>
+        <v>0.9963226318359375</v>
       </c>
     </row>
     <row r="352">
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>0.2550959289073944</v>
+        <v>0.981611430644989</v>
       </c>
     </row>
     <row r="353">
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>0.1779294162988663</v>
+        <v>0.9562341570854187</v>
       </c>
     </row>
     <row r="354">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F354" t="n">
-        <v>0.2305606007575989</v>
+        <v>0.9976958632469177</v>
       </c>
     </row>
     <row r="355">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>0.2418540716171265</v>
+        <v>0.986148476600647</v>
       </c>
     </row>
     <row r="356">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>0.1319667845964432</v>
+        <v>0.9924274086952209</v>
       </c>
     </row>
     <row r="357">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>0.1040356978774071</v>
+        <v>0.9941285848617554</v>
       </c>
     </row>
     <row r="358">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>0.1865752190351486</v>
+        <v>0.9851604700088501</v>
       </c>
     </row>
     <row r="359">
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>0.0527559332549572</v>
+        <v>0.970355749130249</v>
       </c>
     </row>
     <row r="360">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>0.3451578915119171</v>
+        <v>0.9996044039726257</v>
       </c>
     </row>
     <row r="361">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>0.2919493615627289</v>
+        <v>0.9976316690444946</v>
       </c>
     </row>
     <row r="362">
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>0.1954281479120255</v>
+        <v>0.9560548663139343</v>
       </c>
     </row>
     <row r="363">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>0.1902653574943542</v>
+        <v>0.9812116622924805</v>
       </c>
     </row>
     <row r="364">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>0.1456417143344879</v>
+        <v>0.9869927167892456</v>
       </c>
     </row>
     <row r="365">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>0.2480990439653397</v>
+        <v>0.9976778626441956</v>
       </c>
     </row>
     <row r="366">
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>0.2972909808158875</v>
+        <v>0.9181624054908752</v>
       </c>
     </row>
     <row r="367">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>0.1819273233413696</v>
+        <v>0.9984539747238159</v>
       </c>
     </row>
     <row r="368">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>0.00685304356738925</v>
+        <v>0.9580445885658264</v>
       </c>
     </row>
     <row r="369">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>0.1763405203819275</v>
+        <v>0.9697986245155334</v>
       </c>
     </row>
     <row r="370">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>0.08740675449371338</v>
+        <v>0.9934578537940979</v>
       </c>
     </row>
     <row r="371">
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>0.2312185764312744</v>
+        <v>0.9931313395500183</v>
       </c>
     </row>
     <row r="372">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>0.2799672782421112</v>
+        <v>0.9879176020622253</v>
       </c>
     </row>
     <row r="373">
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>0.140300378203392</v>
+        <v>0.9874613881111145</v>
       </c>
     </row>
     <row r="374">
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>0.1073283776640892</v>
+        <v>0.9918240904808044</v>
       </c>
     </row>
     <row r="375">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>0.2130282074213028</v>
+        <v>0.9954812526702881</v>
       </c>
     </row>
     <row r="376">
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>0.2074229419231415</v>
+        <v>0.9972296357154846</v>
       </c>
     </row>
     <row r="377">
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>0.1749565899372101</v>
+        <v>0.9994663596153259</v>
       </c>
     </row>
     <row r="378">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>0.02616214565932751</v>
+        <v>0.9916525483131409</v>
       </c>
     </row>
     <row r="379">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>0.2511019706726074</v>
+        <v>0.9968331456184387</v>
       </c>
     </row>
     <row r="380">
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>0.05622464418411255</v>
+        <v>0.9907958507537842</v>
       </c>
     </row>
     <row r="381">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>0.3696796000003815</v>
+        <v>0.9961082339286804</v>
       </c>
     </row>
     <row r="382">
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>0.009192368946969509</v>
+        <v>0.9646557569503784</v>
       </c>
     </row>
     <row r="383">
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>0.2073825597763062</v>
+        <v>0.9970968961715698</v>
       </c>
     </row>
     <row r="384">
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>0.1732487380504608</v>
+        <v>0.9891567230224609</v>
       </c>
     </row>
     <row r="385">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>0.1625584661960602</v>
+        <v>0.9989481568336487</v>
       </c>
     </row>
     <row r="386">
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>0.009723543189466</v>
+        <v>0.9450843334197998</v>
       </c>
     </row>
     <row r="387">
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>0.1557764559984207</v>
+        <v>0.9963106513023376</v>
       </c>
     </row>
     <row r="388">
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>0.1476608663797379</v>
+        <v>0.991811990737915</v>
       </c>
     </row>
     <row r="389">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>0.0702802762389183</v>
+        <v>0.9314548373222351</v>
       </c>
     </row>
     <row r="390">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="F390" t="n">
-        <v>0.2377938479185104</v>
+        <v>0.9595705270767212</v>
       </c>
     </row>
     <row r="391">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>0.2461837232112885</v>
+        <v>0.9499735236167908</v>
       </c>
     </row>
     <row r="392">
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>0.03151923418045044</v>
+        <v>0.9777719974517822</v>
       </c>
     </row>
     <row r="393">
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>0.130422055721283</v>
+        <v>0.9835730195045471</v>
       </c>
     </row>
     <row r="394">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>0.1071979478001595</v>
+        <v>0.948603093624115</v>
       </c>
     </row>
     <row r="395">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>0.01380795519798994</v>
+        <v>0.9544633030891418</v>
       </c>
     </row>
     <row r="396">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>0.2074229419231415</v>
+        <v>0.9972296357154846</v>
       </c>
     </row>
     <row r="397">
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>0.1073958724737167</v>
+        <v>0.9839463233947754</v>
       </c>
     </row>
     <row r="398">
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>0.06618909537792206</v>
+        <v>0.9814066886901855</v>
       </c>
     </row>
     <row r="399">
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>0.1672966033220291</v>
+        <v>0.999622106552124</v>
       </c>
     </row>
     <row r="400">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>0.02644835971295834</v>
+        <v>0.9844484329223633</v>
       </c>
     </row>
     <row r="401">
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0.1536081433296204</v>
+        <v>0.9989444613456726</v>
       </c>
     </row>
     <row r="402">
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>0.2865982353687286</v>
+        <v>0.9997137188911438</v>
       </c>
     </row>
     <row r="403">
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>0.1586313247680664</v>
+        <v>0.9987897276878357</v>
       </c>
     </row>
     <row r="404">
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>0.1148542389273643</v>
+        <v>0.9991600513458252</v>
       </c>
     </row>
     <row r="405">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>0.2315382361412048</v>
+        <v>0.9992251396179199</v>
       </c>
     </row>
     <row r="406">
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>0.06703667342662811</v>
+        <v>0.9962875843048096</v>
       </c>
     </row>
     <row r="407">
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="F407" t="n">
-        <v>0.09630229324102402</v>
+        <v>0.9789380431175232</v>
       </c>
     </row>
     <row r="408">
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>0.1313909739255905</v>
+        <v>0.9993383288383484</v>
       </c>
     </row>
     <row r="409">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="F409" t="n">
-        <v>0.201327458024025</v>
+        <v>0.994268536567688</v>
       </c>
     </row>
     <row r="410">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>0.2997323870658875</v>
+        <v>0.9968460202217102</v>
       </c>
     </row>
     <row r="411">
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>0.08231737464666367</v>
+        <v>0.9971555471420288</v>
       </c>
     </row>
     <row r="412">
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>0.1148542389273643</v>
+        <v>0.9991600513458252</v>
       </c>
     </row>
     <row r="413">
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>0.2517806887626648</v>
+        <v>0.9895618557929993</v>
       </c>
     </row>
     <row r="414">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="F414" t="n">
-        <v>0.06988013535737991</v>
+        <v>0.9758517742156982</v>
       </c>
     </row>
     <row r="415">
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>0.05074457079172134</v>
+        <v>0.9956933856010437</v>
       </c>
     </row>
     <row r="416">
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>0.09383398294448853</v>
+        <v>0.9985212683677673</v>
       </c>
     </row>
     <row r="417">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>0.1372383832931519</v>
+        <v>0.9925904273986816</v>
       </c>
     </row>
     <row r="418">
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="F418" t="n">
-        <v>0.2244478911161423</v>
+        <v>0.9835588335990906</v>
       </c>
     </row>
     <row r="419">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>0.06620783358812332</v>
+        <v>0.997856080532074</v>
       </c>
     </row>
     <row r="420">
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>0.3712075054645538</v>
+        <v>0.9978756904602051</v>
       </c>
     </row>
     <row r="421">
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="F421" t="n">
-        <v>0.1240255236625671</v>
+        <v>0.9878048896789551</v>
       </c>
     </row>
     <row r="422">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="F422" t="n">
-        <v>0.1157886907458305</v>
+        <v>0.9849678874015808</v>
       </c>
     </row>
     <row r="423">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="F423" t="n">
-        <v>0.1523144096136093</v>
+        <v>0.9877223968505859</v>
       </c>
     </row>
     <row r="424">
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="F424" t="n">
-        <v>0.1863294243812561</v>
+        <v>0.9948843121528625</v>
       </c>
     </row>
     <row r="425">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="F425" t="n">
-        <v>0.05014793947339058</v>
+        <v>0.90434330701828</v>
       </c>
     </row>
     <row r="426">
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>0.2719973027706146</v>
+        <v>0.9908686876296997</v>
       </c>
     </row>
     <row r="427">
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="F427" t="n">
-        <v>0.1504009962081909</v>
+        <v>0.997139573097229</v>
       </c>
     </row>
     <row r="428">
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="F428" t="n">
-        <v>0.1046903058886528</v>
+        <v>0.9883667826652527</v>
       </c>
     </row>
     <row r="429">
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="F429" t="n">
-        <v>0.1356885135173798</v>
+        <v>0.9988780617713928</v>
       </c>
     </row>
     <row r="430">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="F430" t="n">
-        <v>0.2678452432155609</v>
+        <v>0.9893438816070557</v>
       </c>
     </row>
     <row r="431">
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="F431" t="n">
-        <v>0.07442792505025864</v>
+        <v>0.9930520057678223</v>
       </c>
     </row>
     <row r="432">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="F432" t="n">
-        <v>0.2177324593067169</v>
+        <v>0.9992468357086182</v>
       </c>
     </row>
     <row r="433">
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="F433" t="n">
-        <v>0.08951801061630249</v>
+        <v>0.998056173324585</v>
       </c>
     </row>
     <row r="434">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="F434" t="n">
-        <v>0.03267352283000946</v>
+        <v>0.9910626411437988</v>
       </c>
     </row>
     <row r="435">
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>0.05608455464243889</v>
+        <v>0.9883363842964172</v>
       </c>
     </row>
     <row r="436">
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="F436" t="n">
-        <v>0.1154070273041725</v>
+        <v>0.9831757545471191</v>
       </c>
     </row>
     <row r="437">
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>0.1219494193792343</v>
+        <v>0.9975422620773315</v>
       </c>
     </row>
     <row r="438">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>0.2453446090221405</v>
+        <v>0.9528132677078247</v>
       </c>
     </row>
     <row r="439">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="F439" t="n">
-        <v>0.01984666660428047</v>
+        <v>0.9076641798019409</v>
       </c>
     </row>
     <row r="440">
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>0.2579578161239624</v>
+        <v>0.9997017979621887</v>
       </c>
     </row>
     <row r="441">
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>0.006482923403382301</v>
+        <v>0.9547173976898193</v>
       </c>
     </row>
     <row r="442">
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>0.02956157177686691</v>
+        <v>0.9954066276550293</v>
       </c>
     </row>
     <row r="443">
@@ -10181,7 +10181,7 @@
         </is>
       </c>
       <c r="F443" t="n">
-        <v>0.1483974009752274</v>
+        <v>0.9985087513923645</v>
       </c>
     </row>
     <row r="444">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="F444" t="n">
-        <v>0.1951590776443481</v>
+        <v>0.9931538105010986</v>
       </c>
     </row>
     <row r="445">
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="F445" t="n">
-        <v>0.1331918239593506</v>
+        <v>0.998920202255249</v>
       </c>
     </row>
     <row r="446">
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="F446" t="n">
-        <v>0.1654116809368134</v>
+        <v>0.9916911125183105</v>
       </c>
     </row>
     <row r="447">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="F447" t="n">
-        <v>0.05668481066823006</v>
+        <v>0.956378161907196</v>
       </c>
     </row>
     <row r="448">
@@ -10291,7 +10291,7 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>0.06638003140687943</v>
+        <v>0.9908402562141418</v>
       </c>
     </row>
     <row r="449">
@@ -10313,7 +10313,7 @@
         </is>
       </c>
       <c r="F449" t="n">
-        <v>0.02138190530240536</v>
+        <v>0.8490690588951111</v>
       </c>
     </row>
     <row r="450">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="F450" t="n">
-        <v>0.03295047208666801</v>
+        <v>0.8557373285293579</v>
       </c>
     </row>
     <row r="451">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>0.1911844909191132</v>
+        <v>0.9952900409698486</v>
       </c>
     </row>
     <row r="452">
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="F452" t="n">
-        <v>0.09549644589424133</v>
+        <v>0.9602313637733459</v>
       </c>
     </row>
     <row r="453">
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>0.3034954965114594</v>
+        <v>0.9777042865753174</v>
       </c>
     </row>
     <row r="454">
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>0.09991347044706345</v>
+        <v>0.9756798148155212</v>
       </c>
     </row>
     <row r="455">
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>0.1374139189720154</v>
+        <v>0.9757292866706848</v>
       </c>
     </row>
     <row r="456">
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="F456" t="n">
-        <v>0.09236669540405273</v>
+        <v>0.9882346391677856</v>
       </c>
     </row>
     <row r="457">
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>0.138446107506752</v>
+        <v>0.9940811991691589</v>
       </c>
     </row>
     <row r="458">
@@ -10511,7 +10511,7 @@
         </is>
       </c>
       <c r="F458" t="n">
-        <v>0.1651161164045334</v>
+        <v>0.9945504069328308</v>
       </c>
     </row>
     <row r="459">
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>0.1225853115320206</v>
+        <v>0.9819769859313965</v>
       </c>
     </row>
     <row r="460">
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>0.008867288939654827</v>
+        <v>0.9707622528076172</v>
       </c>
     </row>
     <row r="461">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="F461" t="n">
-        <v>0.1593779176473618</v>
+        <v>0.9885391592979431</v>
       </c>
     </row>
     <row r="462">
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>0.02956157177686691</v>
+        <v>0.9954066276550293</v>
       </c>
     </row>
     <row r="463">
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="F463" t="n">
-        <v>0.2530211806297302</v>
+        <v>0.996610701084137</v>
       </c>
     </row>
     <row r="464">
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="F464" t="n">
-        <v>0.2112372517585754</v>
+        <v>0.9907507300376892</v>
       </c>
     </row>
     <row r="465">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="F465" t="n">
-        <v>0.3784769177436829</v>
+        <v>0.9970096349716187</v>
       </c>
     </row>
     <row r="466">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="F466" t="n">
-        <v>0.1538236737251282</v>
+        <v>0.9861302971839905</v>
       </c>
     </row>
     <row r="467">
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="F467" t="n">
-        <v>0.004157838877290487</v>
+        <v>0.9473198056221008</v>
       </c>
     </row>
     <row r="468">
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>0.01535413507372141</v>
+        <v>0.7924525737762451</v>
       </c>
     </row>
     <row r="469">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="F469" t="n">
-        <v>0.04474135115742683</v>
+        <v>0.912777304649353</v>
       </c>
     </row>
     <row r="470">
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="F470" t="n">
-        <v>0.2843632102012634</v>
+        <v>0.9490365386009216</v>
       </c>
     </row>
     <row r="471">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="F471" t="n">
-        <v>0.2008284479379654</v>
+        <v>0.9894914627075195</v>
       </c>
     </row>
     <row r="472">
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>0.009978500194847584</v>
+        <v>0.967412531375885</v>
       </c>
     </row>
     <row r="473">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="F473" t="n">
-        <v>0.1389331668615341</v>
+        <v>0.9987301230430603</v>
       </c>
     </row>
     <row r="474">
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="F474" t="n">
-        <v>0.02098690904676914</v>
+        <v>0.9202228784561157</v>
       </c>
     </row>
     <row r="475">
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="F475" t="n">
-        <v>0.1951943188905716</v>
+        <v>0.9925984144210815</v>
       </c>
     </row>
     <row r="476">
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="F476" t="n">
-        <v>0.4875331819057465</v>
+        <v>0.9767499566078186</v>
       </c>
     </row>
     <row r="477">
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="F477" t="n">
-        <v>0.1864272952079773</v>
+        <v>0.9917803406715393</v>
       </c>
     </row>
     <row r="478">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>0.2511582374572754</v>
+        <v>0.9982341527938843</v>
       </c>
     </row>
     <row r="479">
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="F479" t="n">
-        <v>0.1261893808841705</v>
+        <v>0.9867385625839233</v>
       </c>
     </row>
     <row r="480">
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="F480" t="n">
-        <v>0.009751121513545513</v>
+        <v>0.9222489595413208</v>
       </c>
     </row>
     <row r="481">
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>0.03391687199473381</v>
+        <v>0.9767735004425049</v>
       </c>
     </row>
     <row r="482">
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>0.1888220310211182</v>
+        <v>0.9780585765838623</v>
       </c>
     </row>
     <row r="483">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="F483" t="n">
-        <v>0.03565430268645287</v>
+        <v>0.9489598870277405</v>
       </c>
     </row>
     <row r="484">
@@ -11083,7 +11083,7 @@
         </is>
       </c>
       <c r="F484" t="n">
-        <v>0.1011984050273895</v>
+        <v>0.9993435740470886</v>
       </c>
     </row>
     <row r="485">
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>0.1156893745064735</v>
+        <v>0.99365234375</v>
       </c>
     </row>
     <row r="486">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="F486" t="n">
-        <v>0.02581346593797207</v>
+        <v>0.8696456551551819</v>
       </c>
     </row>
     <row r="487">
@@ -11149,7 +11149,7 @@
         </is>
       </c>
       <c r="F487" t="n">
-        <v>0.03580127283930779</v>
+        <v>0.9492135047912598</v>
       </c>
     </row>
     <row r="488">
@@ -11171,7 +11171,7 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>0.1455355435609818</v>
+        <v>0.9906439781188965</v>
       </c>
     </row>
     <row r="489">
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>0.1268319189548492</v>
+        <v>0.9963194131851196</v>
       </c>
     </row>
     <row r="490">
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="F490" t="n">
-        <v>0.1448794901371002</v>
+        <v>0.9905189871788025</v>
       </c>
     </row>
     <row r="491">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="F491" t="n">
-        <v>0.01684608310461044</v>
+        <v>0.9870460033416748</v>
       </c>
     </row>
     <row r="492">
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="F492" t="n">
-        <v>0.2863654792308807</v>
+        <v>0.9946109056472778</v>
       </c>
     </row>
     <row r="493">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="F493" t="n">
-        <v>0.06105083972215652</v>
+        <v>0.9884535670280457</v>
       </c>
     </row>
     <row r="494">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="F494" t="n">
-        <v>0.1073633283376694</v>
+        <v>0.9940311312675476</v>
       </c>
     </row>
     <row r="495">
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="F495" t="n">
-        <v>0.2194396406412125</v>
+        <v>0.9796372056007385</v>
       </c>
     </row>
     <row r="496">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="F496" t="n">
-        <v>0.07325870543718338</v>
+        <v>0.9805341362953186</v>
       </c>
     </row>
     <row r="497">
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="F497" t="n">
-        <v>0.1605235934257507</v>
+        <v>0.9970141649246216</v>
       </c>
     </row>
     <row r="498">
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="F498" t="n">
-        <v>0.09253626316785812</v>
+        <v>0.9693213701248169</v>
       </c>
     </row>
     <row r="499">
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="F499" t="n">
-        <v>0.02095730789005756</v>
+        <v>0.9816152453422546</v>
       </c>
     </row>
     <row r="500">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>0.05429287627339363</v>
+        <v>0.9924867153167725</v>
       </c>
     </row>
     <row r="501">
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="F501" t="n">
-        <v>0.04540736228227615</v>
+        <v>0.9748154878616333</v>
       </c>
     </row>
     <row r="502">
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="F502" t="n">
-        <v>0.1641986519098282</v>
+        <v>0.8888663053512573</v>
       </c>
     </row>
     <row r="503">
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>0.02271239086985588</v>
+        <v>0.9895063042640686</v>
       </c>
     </row>
     <row r="504">
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="F504" t="n">
-        <v>0.1812232583761215</v>
+        <v>0.9961381554603577</v>
       </c>
     </row>
     <row r="505">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>0.09253626316785812</v>
+        <v>0.9693213701248169</v>
       </c>
     </row>
     <row r="506">
@@ -11567,7 +11567,7 @@
         </is>
       </c>
       <c r="F506" t="n">
-        <v>0.03004230745136738</v>
+        <v>0.9739858508110046</v>
       </c>
     </row>
     <row r="507">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>0.2262707948684692</v>
+        <v>0.988750159740448</v>
       </c>
     </row>
     <row r="508">
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>0.06585516035556793</v>
+        <v>0.9822670817375183</v>
       </c>
     </row>
     <row r="509">
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>0.2739037275314331</v>
+        <v>0.9873824715614319</v>
       </c>
     </row>
     <row r="510">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="F510" t="n">
-        <v>0.428813248872757</v>
+        <v>0.9979967474937439</v>
       </c>
     </row>
     <row r="511">
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="F511" t="n">
-        <v>0.04010463878512383</v>
+        <v>0.9745007753372192</v>
       </c>
     </row>
     <row r="512">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="F512" t="n">
-        <v>0.2067456245422363</v>
+        <v>0.9910976886749268</v>
       </c>
     </row>
     <row r="513">
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="F513" t="n">
-        <v>0.1795627921819687</v>
+        <v>0.9938649535179138</v>
       </c>
     </row>
     <row r="514">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="F514" t="n">
-        <v>0.05516413599252701</v>
+        <v>0.9721174836158752</v>
       </c>
     </row>
     <row r="515">
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="F515" t="n">
-        <v>0.05545917153358459</v>
+        <v>0.9790228009223938</v>
       </c>
     </row>
     <row r="516">
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="F516" t="n">
-        <v>0.05456402525305748</v>
+        <v>0.9024431705474854</v>
       </c>
     </row>
     <row r="517">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="F517" t="n">
-        <v>0.1377650648355484</v>
+        <v>0.8730794191360474</v>
       </c>
     </row>
     <row r="518">
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="F518" t="n">
-        <v>0.2810692191123962</v>
+        <v>0.9926712512969971</v>
       </c>
     </row>
     <row r="519">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>0.1032720953226089</v>
+        <v>0.9909908771514893</v>
       </c>
     </row>
     <row r="520">
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>0.23955437541008</v>
+        <v>0.9988436698913574</v>
       </c>
     </row>
     <row r="521">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="F521" t="n">
-        <v>0.2262707948684692</v>
+        <v>0.988750159740448</v>
       </c>
     </row>
     <row r="522">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>0.007735172286629677</v>
+        <v>0.9713761210441589</v>
       </c>
     </row>
     <row r="523">
@@ -11941,7 +11941,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>0.164347916841507</v>
+        <v>0.9986447691917419</v>
       </c>
     </row>
     <row r="524">
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>0.08385973423719406</v>
+        <v>0.8855582475662231</v>
       </c>
     </row>
     <row r="525">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>0.0757831484079361</v>
+        <v>0.7483248710632324</v>
       </c>
     </row>
     <row r="526">
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="F526" t="n">
-        <v>0.1916417926549911</v>
+        <v>0.998396098613739</v>
       </c>
     </row>
     <row r="527">
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="F527" t="n">
-        <v>0.150182917714119</v>
+        <v>0.7901914715766907</v>
       </c>
     </row>
     <row r="528">
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>0.1848805844783783</v>
+        <v>0.9984332919120789</v>
       </c>
     </row>
     <row r="529">
@@ -12073,7 +12073,7 @@
         </is>
       </c>
       <c r="F529" t="n">
-        <v>0.1749565899372101</v>
+        <v>0.9994663596153259</v>
       </c>
     </row>
     <row r="530">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="F530" t="n">
-        <v>0.03376395255327225</v>
+        <v>0.9768825769424438</v>
       </c>
     </row>
     <row r="531">
@@ -12117,7 +12117,7 @@
         </is>
       </c>
       <c r="F531" t="n">
-        <v>0.2032511681318283</v>
+        <v>0.997774064540863</v>
       </c>
     </row>
     <row r="532">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="F532" t="n">
-        <v>0.2221704721450806</v>
+        <v>0.9739588499069214</v>
       </c>
     </row>
     <row r="533">
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="F533" t="n">
-        <v>0.2291721701622009</v>
+        <v>0.7525745034217834</v>
       </c>
     </row>
     <row r="534">
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="F534" t="n">
-        <v>0.07237651944160461</v>
+        <v>0.9710232615470886</v>
       </c>
     </row>
     <row r="535">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="F535" t="n">
-        <v>0.25515016913414</v>
+        <v>0.9879481196403503</v>
       </c>
     </row>
     <row r="536">
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="F536" t="n">
-        <v>0.01172704715281725</v>
+        <v>0.971169114112854</v>
       </c>
     </row>
     <row r="537">
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>0.03072053752839565</v>
+        <v>0.9247426986694336</v>
       </c>
     </row>
     <row r="538">
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="F538" t="n">
-        <v>0.0233403705060482</v>
+        <v>0.9794256091117859</v>
       </c>
     </row>
     <row r="539">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>0.1977529525756836</v>
+        <v>0.9915308952331543</v>
       </c>
     </row>
     <row r="540">
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="F540" t="n">
-        <v>0.126927450299263</v>
+        <v>0.9226046204566956</v>
       </c>
     </row>
     <row r="541">
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="F541" t="n">
-        <v>0.03052183613181114</v>
+        <v>0.9574369788169861</v>
       </c>
     </row>
     <row r="542">
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="F542" t="n">
-        <v>0.1493044644594193</v>
+        <v>0.9935519695281982</v>
       </c>
     </row>
     <row r="543">
@@ -12381,7 +12381,7 @@
         </is>
       </c>
       <c r="F543" t="n">
-        <v>0.01010404154658318</v>
+        <v>0.9637153148651123</v>
       </c>
     </row>
     <row r="544">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="F544" t="n">
-        <v>0.1196810454130173</v>
+        <v>0.9807165265083313</v>
       </c>
     </row>
     <row r="545">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="F545" t="n">
-        <v>0.01796225644648075</v>
+        <v>0.8100244402885437</v>
       </c>
     </row>
     <row r="546">
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="F546" t="n">
-        <v>0.3019536733627319</v>
+        <v>0.9915509223937988</v>
       </c>
     </row>
     <row r="547">
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="F547" t="n">
-        <v>0.2041874825954437</v>
+        <v>0.9793828725814819</v>
       </c>
     </row>
     <row r="548">
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="F548" t="n">
-        <v>0.1848805844783783</v>
+        <v>0.9984332919120789</v>
       </c>
     </row>
     <row r="549">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="F549" t="n">
-        <v>0.1764202564954758</v>
+        <v>0.9880807399749756</v>
       </c>
     </row>
     <row r="550">
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="F550" t="n">
-        <v>0.08634880930185318</v>
+        <v>0.9910325407981873</v>
       </c>
     </row>
     <row r="551">
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="F551" t="n">
-        <v>0.07416358590126038</v>
+        <v>0.9954417943954468</v>
       </c>
     </row>
     <row r="552">
@@ -12579,7 +12579,7 @@
         </is>
       </c>
       <c r="F552" t="n">
-        <v>0.003894404275342822</v>
+        <v>0.8780398368835449</v>
       </c>
     </row>
     <row r="553">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="F553" t="n">
-        <v>0.04065556451678276</v>
+        <v>0.9762107133865356</v>
       </c>
     </row>
     <row r="554">
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="F554" t="n">
-        <v>0.0618792399764061</v>
+        <v>0.7520017623901367</v>
       </c>
     </row>
     <row r="555">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="F555" t="n">
-        <v>0.111872486770153</v>
+        <v>0.9655511379241943</v>
       </c>
     </row>
     <row r="556">
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="F556" t="n">
-        <v>0.08414166420698166</v>
+        <v>0.9239370226860046</v>
       </c>
     </row>
     <row r="557">
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="F557" t="n">
-        <v>0.04090425372123718</v>
+        <v>0.9940578937530518</v>
       </c>
     </row>
     <row r="558">
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>0.1926433444023132</v>
+        <v>0.9756146669387817</v>
       </c>
     </row>
     <row r="559">
@@ -12733,7 +12733,7 @@
         </is>
       </c>
       <c r="F559" t="n">
-        <v>0.05900923162698746</v>
+        <v>0.9784820675849915</v>
       </c>
     </row>
     <row r="560">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="F560" t="n">
-        <v>0.1573900878429413</v>
+        <v>0.9867332577705383</v>
       </c>
     </row>
     <row r="561">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="F561" t="n">
-        <v>0.2837851047515869</v>
+        <v>0.9948605895042419</v>
       </c>
     </row>
     <row r="562">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="F562" t="n">
-        <v>0.03709143027663231</v>
+        <v>0.8917430639266968</v>
       </c>
     </row>
     <row r="563">
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="F563" t="n">
-        <v>0.05693184584379196</v>
+        <v>0.8598043322563171</v>
       </c>
     </row>
     <row r="564">
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="F564" t="n">
-        <v>0.398509681224823</v>
+        <v>0.9960545301437378</v>
       </c>
     </row>
     <row r="565">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="F565" t="n">
-        <v>0.1012102067470551</v>
+        <v>0.924204409122467</v>
       </c>
     </row>
     <row r="566">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="F566" t="n">
-        <v>0.2828601598739624</v>
+        <v>0.9801726937294006</v>
       </c>
     </row>
     <row r="567">
@@ -12909,7 +12909,7 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>0.1077414304018021</v>
+        <v>0.9854757189750671</v>
       </c>
     </row>
     <row r="568">
@@ -12931,7 +12931,7 @@
         </is>
       </c>
       <c r="F568" t="n">
-        <v>0.1794860810041428</v>
+        <v>0.9531710743904114</v>
       </c>
     </row>
     <row r="569">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="F569" t="n">
-        <v>0.2405063658952713</v>
+        <v>0.9542292952537537</v>
       </c>
     </row>
     <row r="570">
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="F570" t="n">
-        <v>0.04301509633660316</v>
+        <v>0.9620693922042847</v>
       </c>
     </row>
     <row r="571">
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="F571" t="n">
-        <v>0.02739834226667881</v>
+        <v>0.6374109387397766</v>
       </c>
     </row>
     <row r="572">
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="F572" t="n">
-        <v>0.07689113169908524</v>
+        <v>0.9379021525382996</v>
       </c>
     </row>
     <row r="573">
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="F573" t="n">
-        <v>0.296853244304657</v>
+        <v>0.9950792789459229</v>
       </c>
     </row>
     <row r="574">
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>0.07162217050790787</v>
+        <v>0.7984787225723267</v>
       </c>
     </row>
     <row r="575">
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="F575" t="n">
-        <v>0.1141091585159302</v>
+        <v>0.9772461652755737</v>
       </c>
     </row>
     <row r="576">
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="F576" t="n">
-        <v>0.02368175983428955</v>
+        <v>0.969816267490387</v>
       </c>
     </row>
     <row r="577">
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="F577" t="n">
-        <v>0.03391722962260246</v>
+        <v>0.8814808130264282</v>
       </c>
     </row>
     <row r="578">
@@ -13151,7 +13151,7 @@
         </is>
       </c>
       <c r="F578" t="n">
-        <v>0.07691175490617752</v>
+        <v>0.9951171875</v>
       </c>
     </row>
     <row r="579">
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F579" t="n">
-        <v>0.1042127534747124</v>
+        <v>0.7988420128822327</v>
       </c>
     </row>
     <row r="580">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="F580" t="n">
-        <v>0.06574404239654541</v>
+        <v>0.8236987590789795</v>
       </c>
     </row>
     <row r="581">
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="F581" t="n">
-        <v>0.08519601076841354</v>
+        <v>0.8121384382247925</v>
       </c>
     </row>
     <row r="582">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="F582" t="n">
-        <v>0.2441058903932571</v>
+        <v>0.9467208981513977</v>
       </c>
     </row>
     <row r="583">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="F583" t="n">
-        <v>0.1729347854852676</v>
+        <v>0.9817034602165222</v>
       </c>
     </row>
     <row r="584">
@@ -13283,7 +13283,7 @@
         </is>
       </c>
       <c r="F584" t="n">
-        <v>0.1693932116031647</v>
+        <v>0.8521587252616882</v>
       </c>
     </row>
     <row r="585">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="F585" t="n">
-        <v>0.09774832427501678</v>
+        <v>0.9783971905708313</v>
       </c>
     </row>
     <row r="586">
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="F586" t="n">
-        <v>0.260703057050705</v>
+        <v>0.9683005213737488</v>
       </c>
     </row>
     <row r="587">
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="F587" t="n">
-        <v>0.1344911754131317</v>
+        <v>0.9550170302391052</v>
       </c>
     </row>
     <row r="588">
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="F588" t="n">
-        <v>0.03343240544199944</v>
+        <v>0.9552850127220154</v>
       </c>
     </row>
     <row r="589">
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="F589" t="n">
-        <v>0.1995558142662048</v>
+        <v>0.9179232716560364</v>
       </c>
     </row>
     <row r="590">
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="F590" t="n">
-        <v>0.2401724308729172</v>
+        <v>0.9706282615661621</v>
       </c>
     </row>
     <row r="591">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="F591" t="n">
-        <v>0.2114207744598389</v>
+        <v>0.9951038360595703</v>
       </c>
     </row>
     <row r="592">
@@ -13459,7 +13459,7 @@
         </is>
       </c>
       <c r="F592" t="n">
-        <v>0.2933812439441681</v>
+        <v>0.9973888993263245</v>
       </c>
     </row>
     <row r="593">
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="F593" t="n">
-        <v>0.3833287954330444</v>
+        <v>0.9964891672134399</v>
       </c>
     </row>
     <row r="594">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="F594" t="n">
-        <v>0.3924999535083771</v>
+        <v>0.9955641031265259</v>
       </c>
     </row>
     <row r="595">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="F595" t="n">
-        <v>0.2225214391946793</v>
+        <v>0.9987187385559082</v>
       </c>
     </row>
     <row r="596">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="F596" t="n">
-        <v>0.01394271105527878</v>
+        <v>0.9700553417205811</v>
       </c>
     </row>
     <row r="597">
@@ -13569,7 +13569,7 @@
         </is>
       </c>
       <c r="F597" t="n">
-        <v>0.08511922508478165</v>
+        <v>0.9767767786979675</v>
       </c>
     </row>
     <row r="598">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="F598" t="n">
-        <v>0.1948013305664062</v>
+        <v>0.9974985718727112</v>
       </c>
     </row>
     <row r="599">
@@ -13613,7 +13613,7 @@
         </is>
       </c>
       <c r="F599" t="n">
-        <v>0.4758313596248627</v>
+        <v>0.994419276714325</v>
       </c>
     </row>
     <row r="600">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="F600" t="n">
-        <v>0.06800805777311325</v>
+        <v>0.9972758889198303</v>
       </c>
     </row>
     <row r="601">
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="F601" t="n">
-        <v>0.1670393943786621</v>
+        <v>0.9955995082855225</v>
       </c>
     </row>
     <row r="602">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="F602" t="n">
-        <v>0.2123591154813766</v>
+        <v>0.9881343841552734</v>
       </c>
     </row>
     <row r="603">
@@ -13701,7 +13701,7 @@
         </is>
       </c>
       <c r="F603" t="n">
-        <v>0.154825747013092</v>
+        <v>0.994861900806427</v>
       </c>
     </row>
     <row r="604">
@@ -13723,7 +13723,7 @@
         </is>
       </c>
       <c r="F604" t="n">
-        <v>0.1720708459615707</v>
+        <v>0.995745837688446</v>
       </c>
     </row>
     <row r="605">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="F605" t="n">
-        <v>0.2768795192241669</v>
+        <v>0.989862322807312</v>
       </c>
     </row>
     <row r="606">
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="F606" t="n">
-        <v>0.1372169852256775</v>
+        <v>0.994002640247345</v>
       </c>
     </row>
     <row r="607">
@@ -13789,7 +13789,7 @@
         </is>
       </c>
       <c r="F607" t="n">
-        <v>0.4606674015522003</v>
+        <v>0.9987818598747253</v>
       </c>
     </row>
     <row r="608">
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="F608" t="n">
-        <v>0.2607183158397675</v>
+        <v>0.9980417490005493</v>
       </c>
     </row>
     <row r="609">
@@ -13833,7 +13833,7 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>0.3645682036876678</v>
+        <v>0.9932045936584473</v>
       </c>
     </row>
     <row r="610">
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="F610" t="n">
-        <v>0.09993896633386612</v>
+        <v>0.9955405592918396</v>
       </c>
     </row>
     <row r="611">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>0.2105117291212082</v>
+        <v>0.9873901605606079</v>
       </c>
     </row>
     <row r="612">
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="F612" t="n">
-        <v>0.05033880472183228</v>
+        <v>0.9849922657012939</v>
       </c>
     </row>
     <row r="613">
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>0.08594106882810593</v>
+        <v>0.9894372224807739</v>
       </c>
     </row>
     <row r="614">
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>0.1804096102714539</v>
+        <v>0.9977880716323853</v>
       </c>
     </row>
     <row r="615">
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="F615" t="n">
-        <v>0.2165317088365555</v>
+        <v>0.9954839944839478</v>
       </c>
     </row>
     <row r="616">
@@ -13987,7 +13987,7 @@
         </is>
       </c>
       <c r="F616" t="n">
-        <v>0.3052583336830139</v>
+        <v>0.9851934313774109</v>
       </c>
     </row>
     <row r="617">
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="F617" t="n">
-        <v>0.1408029049634933</v>
+        <v>0.974220335483551</v>
       </c>
     </row>
     <row r="618">
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="F618" t="n">
-        <v>0.3677152991294861</v>
+        <v>0.9983634352684021</v>
       </c>
     </row>
     <row r="619">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="F619" t="n">
-        <v>0.1521396636962891</v>
+        <v>0.9882389307022095</v>
       </c>
     </row>
     <row r="620">
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="F620" t="n">
-        <v>0.07684454321861267</v>
+        <v>0.9970255494117737</v>
       </c>
     </row>
     <row r="621">
@@ -14097,7 +14097,7 @@
         </is>
       </c>
       <c r="F621" t="n">
-        <v>0.05381634831428528</v>
+        <v>0.995991051197052</v>
       </c>
     </row>
     <row r="622">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="F622" t="n">
-        <v>0.1445667296648026</v>
+        <v>0.9957382678985596</v>
       </c>
     </row>
     <row r="623">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="F623" t="n">
-        <v>0.1817640215158463</v>
+        <v>0.9958332777023315</v>
       </c>
     </row>
     <row r="624">
@@ -14163,7 +14163,7 @@
         </is>
       </c>
       <c r="F624" t="n">
-        <v>0.2410824298858643</v>
+        <v>0.9820529818534851</v>
       </c>
     </row>
     <row r="625">
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>0.1123137027025223</v>
+        <v>0.9925171136856079</v>
       </c>
     </row>
     <row r="626">
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="F626" t="n">
-        <v>0.1257810443639755</v>
+        <v>0.9827908277511597</v>
       </c>
     </row>
     <row r="627">
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="F627" t="n">
-        <v>0.1517403870820999</v>
+        <v>0.7008641362190247</v>
       </c>
     </row>
     <row r="628">
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>0.1801982372999191</v>
+        <v>0.9985866546630859</v>
       </c>
     </row>
     <row r="629">
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="F629" t="n">
-        <v>0.1905152499675751</v>
+        <v>0.9997217059135437</v>
       </c>
     </row>
     <row r="630">
@@ -14291,7 +14291,7 @@
         </is>
       </c>
       <c r="F630" t="n">
-        <v>0.1719993203878403</v>
+        <v>0.9269014000892639</v>
       </c>
     </row>
     <row r="631">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="F631" t="n">
-        <v>0.3010672330856323</v>
+        <v>0.9433411359786987</v>
       </c>
     </row>
     <row r="632">
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="F632" t="n">
-        <v>0.6076322197914124</v>
+        <v>0.9930612444877625</v>
       </c>
     </row>
     <row r="633">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>0.0784756988286972</v>
+        <v>0.976504921913147</v>
       </c>
     </row>
     <row r="634">
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>0.2357868850231171</v>
+        <v>0.9481565356254578</v>
       </c>
     </row>
     <row r="635">
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="F635" t="n">
-        <v>0.308970034122467</v>
+        <v>0.9631373882293701</v>
       </c>
     </row>
     <row r="636">
@@ -14411,7 +14411,7 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>0.1718206107616425</v>
+        <v>0.9977890253067017</v>
       </c>
     </row>
   </sheetData>
